--- a/per-stock/SMCI/financials.xlsx
+++ b/per-stock/SMCI/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18668029952</v>
+        <v>19833126912</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26514313216</v>
+        <v>26285774848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.336843</v>
+        <v>16.136843</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.639662</v>
+        <v>9.667014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.55394405</v>
+        <v>0.5885165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-7448383488</v>
+        <v>-6849681000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>601418482</v>
+        <v>646873027</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31.04</v>
+        <v>30.66</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D33</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C33</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B33</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B35:E35)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B8:E8)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1628,13 +2108,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1644,7 +2124,6 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1683,11 +2162,6 @@
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>2024-09-30</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1695,7 +2169,9 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
@@ -1708,10 +2184,7 @@
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1719,7 +2192,9 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>0.207682</v>
+      </c>
       <c r="C3" s="3" t="n">
         <v>0.19822</v>
       </c>
@@ -1730,12 +2205,9 @@
         <v>0.086685</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.151898</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
+        <v>0.05078</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1743,7 +2215,9 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="n">
+        <v>698384000</v>
+      </c>
       <c r="C4" s="3" t="n">
         <v>547982000</v>
       </c>
@@ -1756,10 +2230,7 @@
       <c r="F4" s="3" t="n">
         <v>143627000</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>393972000</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1767,7 +2238,9 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C5" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -1780,10 +2253,7 @@
       <c r="F5" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1791,7 +2261,9 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="n">
+        <v>22932000</v>
+      </c>
       <c r="C6" s="3" t="n">
         <v>22417000</v>
       </c>
@@ -1804,10 +2276,7 @@
       <c r="F6" s="3" t="n">
         <v>15160000</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>12389000</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1815,7 +2284,9 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>9224334000</v>
+      </c>
       <c r="C7" s="3" t="n">
         <v>11883924000</v>
       </c>
@@ -1828,10 +2299,7 @@
       <c r="F7" s="3" t="n">
         <v>4159695000</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>5007940000</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1839,7 +2307,9 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="n">
+        <v>698384000</v>
+      </c>
       <c r="C8" s="3" t="n">
         <v>547982000</v>
       </c>
@@ -1852,10 +2322,7 @@
       <c r="F8" s="3" t="n">
         <v>143627000</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>393972000</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1863,7 +2330,9 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
+      <c r="B9" s="3" t="n">
+        <v>675452000</v>
+      </c>
       <c r="C9" s="3" t="n">
         <v>525565000</v>
       </c>
@@ -1876,10 +2345,7 @@
       <c r="F9" s="3" t="n">
         <v>128467000</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>381583000</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1887,7 +2353,9 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="n">
+        <v>-19046000</v>
+      </c>
       <c r="C10" s="3" t="n">
         <v>25684000</v>
       </c>
@@ -1898,12 +2366,9 @@
         <v>-22282000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-13402000</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2241000</v>
-      </c>
-      <c r="H10" s="3" t="n"/>
+        <v>1252000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1911,7 +2376,9 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>64483000</v>
+      </c>
       <c r="C11" s="3" t="n">
         <v>25358000</v>
       </c>
@@ -1924,10 +2391,7 @@
       <c r="F11" s="3" t="n">
         <v>13402000</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>6535000</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1935,17 +2399,20 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>45437000</v>
+      </c>
       <c r="C12" s="3" t="n">
         <v>51042000</v>
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="F12" s="3" t="n">
+        <v>14654000</v>
+      </c>
       <c r="G12" s="3" t="n">
         <v>8776000</v>
       </c>
-      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1953,7 +2420,9 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C13" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -1966,10 +2435,7 @@
       <c r="F13" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1977,7 +2443,9 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C14" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -1990,10 +2458,7 @@
       <c r="F14" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2001,7 +2466,9 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="n">
+        <v>9617146000</v>
+      </c>
       <c r="C15" s="3" t="n">
         <v>12208193000</v>
       </c>
@@ -2014,10 +2481,7 @@
       <c r="F15" s="3" t="n">
         <v>4453133000</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>5309338000</v>
-      </c>
-      <c r="H15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2025,7 +2489,9 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="3" t="n">
+        <v>625868000</v>
+      </c>
       <c r="C16" s="3" t="n">
         <v>474298000</v>
       </c>
@@ -2038,10 +2504,7 @@
       <c r="F16" s="3" t="n">
         <v>146780000</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>368624000</v>
-      </c>
-      <c r="H16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2065,7 +2528,6 @@
         <v>621809000</v>
       </c>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2089,7 +2551,6 @@
         <v>595041000</v>
       </c>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2113,7 +2574,6 @@
         <v>0.17</v>
       </c>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2137,7 +2597,6 @@
         <v>0.18</v>
       </c>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2145,7 +2604,9 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
+      <c r="B21" s="3" t="n">
+        <v>501275000</v>
+      </c>
       <c r="C21" s="3" t="n">
         <v>418452000</v>
       </c>
@@ -2158,10 +2619,7 @@
       <c r="F21" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>321706000</v>
-      </c>
-      <c r="H21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2169,7 +2627,9 @@
           <t>Average Dilution Earnings</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>17888000</v>
+      </c>
       <c r="C22" s="3" t="n">
         <v>17888000</v>
       </c>
@@ -2183,9 +2643,6 @@
       <c r="G22" s="3" t="n">
         <v>1110000</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>2749000</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2193,7 +2650,9 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C23" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -2206,10 +2665,7 @@
       <c r="F23" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2217,7 +2673,9 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C24" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -2230,10 +2688,7 @@
       <c r="F24" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2241,7 +2696,9 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
+      <c r="B25" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C25" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -2254,10 +2711,7 @@
       <c r="F25" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2265,7 +2719,9 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>483387000</v>
+      </c>
       <c r="C26" s="3" t="n">
         <v>400564000</v>
       </c>
@@ -2278,10 +2734,7 @@
       <c r="F26" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>320596000</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2289,7 +2742,9 @@
           <t>Earnings From Equity Interest Net Of Tax</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>-695000</v>
+      </c>
       <c r="C27" s="3" t="n">
         <v>-492000</v>
       </c>
@@ -2302,10 +2757,7 @@
       <c r="F27" s="3" t="n">
         <v>-445000</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>2517000</v>
-      </c>
-      <c r="H27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2313,7 +2765,9 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>126887000</v>
+      </c>
       <c r="C28" s="3" t="n">
         <v>99151000</v>
       </c>
@@ -2326,10 +2780,7 @@
       <c r="F28" s="3" t="n">
         <v>5843000</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>56969000</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2337,7 +2788,9 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
+      <c r="B29" s="3" t="n">
+        <v>610969000</v>
+      </c>
       <c r="C29" s="3" t="n">
         <v>500207000</v>
       </c>
@@ -2350,10 +2803,7 @@
       <c r="F29" s="3" t="n">
         <v>115065000</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>375048000</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2361,7 +2811,9 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="B30" s="3" t="n">
+        <v>4147000</v>
+      </c>
       <c r="C30" s="3" t="n">
         <v>225000</v>
       </c>
@@ -2372,12 +2824,9 @@
         <v>16616000</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-18313000</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>4183000</v>
-      </c>
-      <c r="H30" s="3" t="n"/>
+        <v>-32967000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2385,7 +2834,9 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>4147000</v>
+      </c>
       <c r="C31" s="3" t="n">
         <v>225000</v>
       </c>
@@ -2396,12 +2847,9 @@
         <v>16616000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-18313000</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>4183000</v>
-      </c>
-      <c r="H31" s="3" t="n"/>
+        <v>-32967000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2409,7 +2857,9 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
+      <c r="B32" s="3" t="n">
+        <v>-19046000</v>
+      </c>
       <c r="C32" s="3" t="n">
         <v>25684000</v>
       </c>
@@ -2420,12 +2870,9 @@
         <v>-22282000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-13402000</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>2241000</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+        <v>1252000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2433,7 +2880,9 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>64483000</v>
+      </c>
       <c r="C33" s="3" t="n">
         <v>25358000</v>
       </c>
@@ -2446,10 +2895,7 @@
       <c r="F33" s="3" t="n">
         <v>13402000</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>6535000</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2457,17 +2903,20 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
+      <c r="B34" s="3" t="n">
+        <v>45437000</v>
+      </c>
       <c r="C34" s="3" t="n">
         <v>51042000</v>
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>14654000</v>
+      </c>
       <c r="G34" s="3" t="n">
         <v>8776000</v>
       </c>
-      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2475,7 +2924,9 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>625868000</v>
+      </c>
       <c r="C35" s="3" t="n">
         <v>474298000</v>
       </c>
@@ -2488,10 +2939,7 @@
       <c r="F35" s="3" t="n">
         <v>146780000</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>368624000</v>
-      </c>
-      <c r="H35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2499,7 +2947,9 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>392812000</v>
+      </c>
       <c r="C36" s="3" t="n">
         <v>324269000</v>
       </c>
@@ -2512,10 +2962,7 @@
       <c r="F36" s="3" t="n">
         <v>293438000</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>301398000</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2523,7 +2970,9 @@
           <t>Research And Development</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
+      <c r="B37" s="3" t="n">
+        <v>215659000</v>
+      </c>
       <c r="C37" s="3" t="n">
         <v>180761000</v>
       </c>
@@ -2536,10 +2985,7 @@
       <c r="F37" s="3" t="n">
         <v>162857000</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>158229000</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2547,7 +2993,9 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
+      <c r="B38" s="3" t="n">
+        <v>177153000</v>
+      </c>
       <c r="C38" s="3" t="n">
         <v>143508000</v>
       </c>
@@ -2560,10 +3008,7 @@
       <c r="F38" s="3" t="n">
         <v>130581000</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>143169000</v>
-      </c>
-      <c r="H38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2571,7 +3016,9 @@
           <t>Selling And Marketing Expense</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
+      <c r="B39" s="3" t="n">
+        <v>89510000</v>
+      </c>
       <c r="C39" s="3" t="n">
         <v>73078000</v>
       </c>
@@ -2584,10 +3031,7 @@
       <c r="F39" s="3" t="n">
         <v>59978000</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>79568000</v>
-      </c>
-      <c r="H39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2595,7 +3039,9 @@
           <t>General And Administrative Expense</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
+      <c r="B40" s="3" t="n">
+        <v>87643000</v>
+      </c>
       <c r="C40" s="3" t="n">
         <v>70430000</v>
       </c>
@@ -2608,10 +3054,7 @@
       <c r="F40" s="3" t="n">
         <v>70603000</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>63601000</v>
-      </c>
-      <c r="H40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2619,7 +3062,9 @@
           <t>Other Gand A</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
+      <c r="B41" s="3" t="n">
+        <v>87643000</v>
+      </c>
       <c r="C41" s="3" t="n">
         <v>70430000</v>
       </c>
@@ -2632,10 +3077,7 @@
       <c r="F41" s="3" t="n">
         <v>70603000</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>63601000</v>
-      </c>
-      <c r="H41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2643,7 +3085,9 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>1018680000</v>
+      </c>
       <c r="C42" s="3" t="n">
         <v>798567000</v>
       </c>
@@ -2656,10 +3100,7 @@
       <c r="F42" s="3" t="n">
         <v>440218000</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>670022000</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2667,7 +3108,9 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
+      <c r="B43" s="3" t="n">
+        <v>9224334000</v>
+      </c>
       <c r="C43" s="3" t="n">
         <v>11883924000</v>
       </c>
@@ -2680,10 +3123,7 @@
       <c r="F43" s="3" t="n">
         <v>4159695000</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>5007940000</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2691,7 +3131,9 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
+      <c r="B44" s="3" t="n">
+        <v>10243014000</v>
+      </c>
       <c r="C44" s="3" t="n">
         <v>12682491000</v>
       </c>
@@ -2704,10 +3146,7 @@
       <c r="F44" s="3" t="n">
         <v>4599913000</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>5677962000</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2715,7 +3154,9 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
+      <c r="B45" s="3" t="n">
+        <v>10243014000</v>
+      </c>
       <c r="C45" s="3" t="n">
         <v>12682491000</v>
       </c>
@@ -2728,17 +3169,14 @@
       <c r="F45" s="3" t="n">
         <v>4599913000</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>5677962000</v>
-      </c>
-      <c r="H45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4318,7 +4756,1823 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>601377832</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>598925891</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>596837343</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>594136852</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>596765126</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>601377832</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>598925891</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>596837343</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>594136852</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>596765126</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>7482777000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>786753000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>578839000</v>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n">
+        <v>479033000</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>170000000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8805804000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4909659000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4805788000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4778842000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2505482000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>7575430000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6992015000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>6523390000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6301693000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6379319000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>16348531000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>11869851000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>11299096000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>11059346000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>8871613000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>13445651000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>10727889000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>10314099000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>9956862000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>8085453000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>7575430000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>6992015000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>6523390000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>6301693000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6379319000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>32703000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>31823000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>30082000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>21189000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>13188000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>7575430000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>6992015000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>6523390000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>6301693000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>6379319000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>14253462000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>11668075000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>11198478000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>10984286000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>8807642000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>7575591000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>6992177000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>6523560000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>6301871000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>6379479000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>161000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>162000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>7575430000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>6992015000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>6523390000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>6301693000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>6379319000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>692000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>695000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>698000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>705000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>663000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>692000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>695000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>698000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>705000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>663000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>4486775000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4003388000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>3602824000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>3434539000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3439380000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>3087963000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2987932000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2919868000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2866449000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2939276000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>3087963000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2987932000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2919868000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2866449000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2939276000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>15876438000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>21009433000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>7862477000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7716558000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>4359046000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>7753803000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>5612725000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>5515242000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>5371766000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2930910000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>411867000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>408098000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>409015000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>326528000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>189593000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dueto Related Parties Non Current</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>494000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>658000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>457000</v>
+      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>663410000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>527909000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>430682000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>362645000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>312994000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>663410000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>527909000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>430682000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>362645000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>312994000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>6678032000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4676060000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>4675088000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>4682593000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2428323000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>6678032000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>4676060000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>4675088000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>4682593000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2428323000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>8122635000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>15396708000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>2347235000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2344792000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1428136000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1675805000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>896878000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>644353000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>628868000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>405757000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1675805000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>896878000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>644353000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>628868000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>405757000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>2127772000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>233599000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>130700000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>96249000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>77159000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>32703000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>31823000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>30082000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>21189000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>13188000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2095069000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>201776000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>100618000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>75060000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>63971000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2095069000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>34453000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>43077000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>75060000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>63971000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>167323000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>57541000</v>
+      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>154988000</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>493808000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>4319058000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>14266231000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1572182000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1619675000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>945220000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>453265000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>274512000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>216725000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>245156000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>236238000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>103846000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>27388000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>8356000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>27701000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>10011000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>3865793000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>13991719000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1355457000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1374519000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>708982000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>178802000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>238512000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>75790000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>92542000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>65932000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>38333000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>118700000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>56235000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>53381000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>23633000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>3686991000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>13753207000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1279667000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>1281977000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>643050000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>23452029000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>28001610000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>14386037000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>14018429000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>10738525000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1883743000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1877013000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1724703000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1716775000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1224936000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>39546000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>33399000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>18725000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>16714000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>251155000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>3896000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3669000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>4528000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>4980000</v>
+      </c>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>643879000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>666850000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>628085000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>618129000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>481216000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>632715000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>655367000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>617257000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>607416000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>481216000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>87733000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>141128000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>76355000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>166405000</v>
+      </c>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>139593000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>123288000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>100330000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>112367000</v>
+      </c>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n">
+        <v>112367000</v>
+      </c>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>969096000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>908679000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>896680000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>798180000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>492565000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>-155825000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>-142458000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>-129755000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-118245000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>-241988000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1124921000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1051137000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1026435000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>916425000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>734553000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>55705000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>11527000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1275000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1038000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>669000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>361437000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>370095000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>375968000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>293692000</v>
+      </c>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>191484000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>181232000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>166762000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>154716000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>269100000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>322878000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>315955000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>310228000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>304131000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>301821000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>193417000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>172328000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>172202000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>162848000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>162963000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>21568286000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>26124597000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>12661334000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>12301654000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>9513589000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>732476000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>433312000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>208224000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>233681000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>449968000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>11103376000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>10595448000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>5730002000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>4680375000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>3870243000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>8154074000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>7510625000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>3877754000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>3465352000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2870043000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1991524000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>2331526000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1259183000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>674613000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>454396000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>957778000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>753297000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>593065000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>540410000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>545804000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>8442110000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>11004754000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2526241000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2217687000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2657277000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Duefrom Related Parties Current</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>28714000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>632000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1202000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>13745000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>14721000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>8413396000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>11004122000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2525039000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>2203942000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2642556000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>-488000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>-572000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>-533000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>-67000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>8413884000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>11004694000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2525572000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2203942000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>2642623000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>1290324000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>4091083000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>4196867000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>5169911000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2536101000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>1290324000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4091083000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>4196867000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>5169911000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2536101000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5614,13 +7868,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5630,6 +7884,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5640,30 +7895,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5676,21 +7936,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-6695704000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-45119000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-949793000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>840935000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>594064000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-267293000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5699,21 +7960,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-101677000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-111851000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-11540000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-37284000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-157307000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-467881000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5722,21 +7984,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3996465000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>210212000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>28588000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>2285973000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>734910000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>121743000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5746,14 +8009,15 @@
       </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5762,21 +8026,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-80278000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-21221000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-32270000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-22678000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-32700000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-27536000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5785,21 +8050,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>40823000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1226000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>39244000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1444000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>5040000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>7552000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5808,21 +8074,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>179820000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>52072000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>38502000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>56766000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>213363000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>53693000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5831,21 +8098,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1339966000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>4193725000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>4199255000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>5172301000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>2537092000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>1430987000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5854,21 +8122,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>4193725000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>4199255000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>5172301000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>2537092000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>1430987000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>2089231000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5877,21 +8146,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-393000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-1573000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-4588000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>847000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-11000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-3663000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5900,21 +8170,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-2853366000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-3957000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-968458000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>2634362000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>1106116000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-654581000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5923,21 +8194,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>3859338000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>66162000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-18665000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>1849427000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>512052000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-387288000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5946,21 +8218,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>3859338000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>66162000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-18665000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>1849427000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>512052000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-387288000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5969,21 +8242,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-40872000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-37202000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-43635000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-205708000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-73134000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-41492000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5992,21 +8266,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>5422000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>5003000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>7922000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>6446000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>7583000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>342000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6016,14 +8291,15 @@
       </c>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n">
         <v>-200000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6033,14 +8309,15 @@
       </c>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="3" t="n"/>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6049,21 +8326,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>3894788000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>98361000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>17048000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>2248689000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>577603000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-346138000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6072,15 +8350,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>17048000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-7284000</v>
       </c>
-      <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>78856000</v>
       </c>
     </row>
@@ -6091,15 +8370,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>-11540000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-37284000</v>
       </c>
-      <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>-1106178000</v>
       </c>
     </row>
@@ -6110,15 +8390,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
         <v>28588000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>30000000</v>
       </c>
-      <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n">
         <v>1185034000</v>
       </c>
     </row>
@@ -6128,16 +8409,19 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>-115409000</v>
+      </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n">
         <v>2255973000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>950978000</v>
       </c>
-      <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6145,16 +8429,19 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>-238800000</v>
+      </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n">
         <v>2255973000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-623081000</v>
       </c>
-      <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6163,21 +8450,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-97278000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-46221000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-32270000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-78678000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-32700000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-27536000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6186,21 +8474,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-97278000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-46221000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-32270000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-78678000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-32700000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-27536000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6208,13 +8497,13 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>-17000000</v>
+      </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n">
         <v>-56000000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
@@ -6222,6 +8511,9 @@
       <c r="G27" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H27" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6229,13 +8521,13 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>-17000000</v>
+      </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n">
         <v>-56000000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -6243,6 +8535,9 @@
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6251,21 +8546,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-80278000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-21221000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-32270000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-22678000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-32700000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-27536000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6274,21 +8570,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-80278000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-21221000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-32270000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-22678000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-32700000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-27536000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6297,21 +8594,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-6615426000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-23898000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-917523000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>863613000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>626764000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-239757000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6320,21 +8618,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-6615426000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>-23898000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>-917523000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>863613000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>626764000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-239757000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6343,21 +8642,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-7342956000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-637603000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-1227845000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>620480000</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>471453000</v>
-      </c>
       <c r="F33" s="3" t="n">
-        <v>-648188000</v>
+        <v>312403000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6366,21 +8666,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>832889000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>274751000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>296622000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>65585000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>67145000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>40470000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6389,21 +8690,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>11660000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>5362000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>3171000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-2500000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>1341000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>2553000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6412,21 +8714,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-9866878000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>12748619000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-253471000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>877090000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>116114000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-1177492000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6435,21 +8738,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>272577000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>219689000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-259350000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>219690000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>112368000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-85628000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6458,21 +8762,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-10139455000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>12528930000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>5879000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>657400000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>3746000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>-1091864000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6481,21 +8786,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-10059838000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>12465867000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>901000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>630722000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>95226000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-1127269000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6504,21 +8810,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-79617000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>63063000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>4978000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>26678000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-91480000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>35405000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6527,21 +8834,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-79617000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>63063000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>4978000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>26678000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-91480000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>35405000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6550,21 +8858,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-322883000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-192942000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>134087000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>55249000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>114413000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-485543000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6573,21 +8882,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-580741000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-5001809000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-1087010000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-813503000</v>
       </c>
-      <c r="E43" s="3" t="n">
-        <v>-241716000</v>
-      </c>
       <c r="F43" s="3" t="n">
-        <v>1306486000</v>
+        <v>-400766000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6596,21 +8906,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>2582997000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-8471584000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-321244000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>438559000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>414156000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-334662000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6619,21 +8930,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>2582997000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-8471584000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-321244000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>438559000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>414156000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-334662000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6642,21 +8954,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>8059000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>3597000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>-2796000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>1614000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>5287000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>1715000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6665,21 +8978,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>125934000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>90485000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>89139000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>83612000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>84704000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>82122000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6688,19 +9002,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>70155000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>134648000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>48199000</v>
       </c>
-      <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n">
+        <v>125018000</v>
+      </c>
+      <c r="G48" s="3" t="n">
         <v>24876000</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>9156000</v>
-      </c>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6709,21 +9026,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>20955000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-39674000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-12201000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-80237000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-58323000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-29526000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6732,21 +9050,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>20955000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-39674000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-12201000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-80237000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-58323000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-29526000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6755,21 +9074,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>22932000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>22417000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>20607000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>18636000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>15160000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>12389000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6778,21 +9098,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>22932000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>22417000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>20607000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>18636000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>15160000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>12389000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6801,19 +9122,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>22932000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>22417000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>20607000</v>
       </c>
-      <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n">
+        <v>15160000</v>
+      </c>
+      <c r="G53" s="3" t="n">
         <v>12389000</v>
       </c>
-      <c r="G53" s="3" t="n">
-        <v>12159000</v>
-      </c>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6822,21 +9146,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>-3892000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>1668000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>-911000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>24354000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>33738000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>-3741000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6845,21 +9170,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>695000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>492000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>106000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>8264000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>445000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>-2517000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6868,21 +9194,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>-4587000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>1176000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>-1017000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>16090000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>3042000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>-1224000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6891,28 +9218,29 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>483387000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>400564000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>168285000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>195154000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>108777000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>320596000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
